--- a/cls.var_AMR_ville_FQ_R.xlsx
+++ b/cls.var_AMR_ville_FQ_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prescri_1</t>
   </si>
   <si>
     <t xml:space="preserve">AMR_animaux_compagnie_C3G_R</t>
@@ -619,7 +622,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -691,7 +694,7 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -707,7 +710,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -731,15 +734,15 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
         <v>30</v>
-      </c>
-      <c r="B27" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -747,7 +750,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -755,15 +758,15 @@
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
         <v>34</v>
-      </c>
-      <c r="B30" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -771,7 +774,7 @@
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -779,7 +782,7 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
@@ -787,7 +790,7 @@
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -795,7 +798,7 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
@@ -803,7 +806,7 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
@@ -811,7 +814,7 @@
         <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
@@ -819,7 +822,7 @@
         <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38">
@@ -827,7 +830,7 @@
         <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
@@ -835,7 +838,7 @@
         <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
@@ -843,7 +846,7 @@
         <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
@@ -851,7 +854,7 @@
         <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -859,7 +862,7 @@
         <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -875,7 +878,7 @@
         <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -899,7 +902,7 @@
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -915,7 +918,7 @@
         <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -931,7 +934,7 @@
         <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -939,7 +942,7 @@
         <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -979,6 +982,14 @@
         <v>61</v>
       </c>
       <c r="B57" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" t="s">
         <v>6</v>
       </c>
     </row>
